--- a/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Backtrace_Start_tob_de.xlsx
+++ b/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Backtrace_Start_tob_de.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDF8AE0F-0A92-4392-B107-FD8876430B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="25215" windowHeight="5745"/>
+    <workbookView xWindow="1005" yWindow="1995" windowWidth="28695" windowHeight="15075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rückverfolgung" sheetId="5" r:id="rId1"/>
@@ -12,7 +13,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Rückverfolgung!$A$1:$M$40</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -109,13 +121,13 @@
     <t>[Betriebsart]</t>
   </si>
   <si>
-    <t>Bei Rückfragen bitte einfach Kontakt aufnehmen mit dem BfR FoodRiskLabs-Team, +49 (30) 18412-4444, foodrisklabs@bfr.bund.de</t>
+    <t>Bei Rückfragen bitte das BfR FoodRiskLabs-Team per E-Mail kontaktieren: foodrisklabs@bfr.bund.de</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1495,6 +1507,72 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="29" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="29" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="33" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1559,188 +1637,122 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="29" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="29" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="114">
-    <cellStyle name="20% - Accent1 2" xfId="4"/>
-    <cellStyle name="20% - Accent2 2" xfId="5"/>
-    <cellStyle name="20% - Accent3 2" xfId="6"/>
-    <cellStyle name="20% - Accent4 2" xfId="7"/>
-    <cellStyle name="20% - Accent5 2" xfId="8"/>
-    <cellStyle name="20% - Accent6 2" xfId="9"/>
-    <cellStyle name="40% - Accent1 2" xfId="10"/>
-    <cellStyle name="40% - Accent2 2" xfId="11"/>
-    <cellStyle name="40% - Accent3 2" xfId="12"/>
-    <cellStyle name="40% - Accent4 2" xfId="13"/>
-    <cellStyle name="40% - Accent5 2" xfId="14"/>
-    <cellStyle name="40% - Accent6 2" xfId="15"/>
-    <cellStyle name="60% - Accent1 2" xfId="16"/>
-    <cellStyle name="60% - Accent2 2" xfId="17"/>
-    <cellStyle name="60% - Accent3 2" xfId="18"/>
-    <cellStyle name="60% - Accent4 2" xfId="19"/>
-    <cellStyle name="60% - Accent5 2" xfId="20"/>
-    <cellStyle name="60% - Accent6 2" xfId="21"/>
-    <cellStyle name="Accent1 2" xfId="22"/>
-    <cellStyle name="Accent2 2" xfId="23"/>
-    <cellStyle name="Accent3 2" xfId="24"/>
-    <cellStyle name="Accent4 2" xfId="25"/>
-    <cellStyle name="Accent5 2" xfId="26"/>
-    <cellStyle name="Accent6 2" xfId="27"/>
-    <cellStyle name="Bad 2" xfId="28"/>
-    <cellStyle name="Calculation 2" xfId="29"/>
-    <cellStyle name="Check Cell 2" xfId="30"/>
-    <cellStyle name="Explanatory Text 2" xfId="31"/>
-    <cellStyle name="Good 2" xfId="32"/>
-    <cellStyle name="Heading 1 2" xfId="33"/>
-    <cellStyle name="Heading 2 2" xfId="34"/>
-    <cellStyle name="Heading 3 2" xfId="35"/>
-    <cellStyle name="Heading 4 2" xfId="36"/>
-    <cellStyle name="Input 2" xfId="37"/>
-    <cellStyle name="Linked Cell 2" xfId="38"/>
-    <cellStyle name="Neutral 2" xfId="39"/>
-    <cellStyle name="Normal 10" xfId="40"/>
-    <cellStyle name="Normal 10 2" xfId="41"/>
-    <cellStyle name="Normal 10 2 2" xfId="42"/>
-    <cellStyle name="Normal 10 2 3" xfId="43"/>
-    <cellStyle name="Normal 10 3" xfId="44"/>
-    <cellStyle name="Normal 10 4" xfId="45"/>
-    <cellStyle name="Normal 11" xfId="46"/>
-    <cellStyle name="Normal 11 2" xfId="47"/>
-    <cellStyle name="Normal 11 2 2" xfId="48"/>
-    <cellStyle name="Normal 11 2 3" xfId="49"/>
-    <cellStyle name="Normal 11 3" xfId="50"/>
-    <cellStyle name="Normal 11 4" xfId="51"/>
-    <cellStyle name="Normal 12" xfId="52"/>
-    <cellStyle name="Normal 12 2" xfId="53"/>
-    <cellStyle name="Normal 12 3" xfId="54"/>
-    <cellStyle name="Normal 12 4" xfId="55"/>
-    <cellStyle name="Normal 13" xfId="56"/>
-    <cellStyle name="Normal 13 2" xfId="57"/>
-    <cellStyle name="Normal 13 3" xfId="58"/>
-    <cellStyle name="Normal 13 4" xfId="59"/>
-    <cellStyle name="Normal 14" xfId="60"/>
-    <cellStyle name="Normal 14 2" xfId="61"/>
-    <cellStyle name="Normal 15" xfId="62"/>
-    <cellStyle name="Normal 15 2" xfId="63"/>
-    <cellStyle name="Normal 16" xfId="64"/>
-    <cellStyle name="Normal 17" xfId="65"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="67"/>
-    <cellStyle name="Normal 2 2 2" xfId="68"/>
-    <cellStyle name="Normal 2 2 3" xfId="69"/>
-    <cellStyle name="Normal 2 3" xfId="70"/>
-    <cellStyle name="Normal 2 3 2" xfId="71"/>
-    <cellStyle name="Normal 2 3 3" xfId="72"/>
-    <cellStyle name="Normal 2 4" xfId="73"/>
-    <cellStyle name="Normal 2 5" xfId="74"/>
-    <cellStyle name="Normal 2 6" xfId="66"/>
-    <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="76"/>
-    <cellStyle name="Normal 3 3" xfId="77"/>
-    <cellStyle name="Normal 3 4" xfId="75"/>
-    <cellStyle name="Normal 4" xfId="78"/>
-    <cellStyle name="Normal 4 2" xfId="79"/>
-    <cellStyle name="Normal 4 3" xfId="80"/>
-    <cellStyle name="Normal 5" xfId="81"/>
-    <cellStyle name="Normal 6" xfId="82"/>
-    <cellStyle name="Normal 6 2" xfId="83"/>
-    <cellStyle name="Normal 6 3" xfId="84"/>
-    <cellStyle name="Normal 7" xfId="85"/>
-    <cellStyle name="Normal 7 2" xfId="86"/>
-    <cellStyle name="Normal 7 2 2" xfId="87"/>
-    <cellStyle name="Normal 7 2 3" xfId="88"/>
-    <cellStyle name="Normal 7 3" xfId="89"/>
-    <cellStyle name="Normal 7 3 2" xfId="90"/>
-    <cellStyle name="Normal 7 3 3" xfId="91"/>
-    <cellStyle name="Normal 7 4" xfId="92"/>
-    <cellStyle name="Normal 7 5" xfId="93"/>
-    <cellStyle name="Normal 8" xfId="94"/>
-    <cellStyle name="Normal 8 2" xfId="95"/>
-    <cellStyle name="Normal 8 2 2" xfId="96"/>
-    <cellStyle name="Normal 8 2 3" xfId="97"/>
-    <cellStyle name="Normal 8 3" xfId="98"/>
-    <cellStyle name="Normal 8 4" xfId="99"/>
-    <cellStyle name="Normal 9" xfId="100"/>
-    <cellStyle name="Normal 9 2" xfId="101"/>
-    <cellStyle name="Normal 9 2 2" xfId="102"/>
-    <cellStyle name="Normal 9 2 3" xfId="103"/>
-    <cellStyle name="Normal 9 3" xfId="104"/>
-    <cellStyle name="Normal 9 4" xfId="105"/>
-    <cellStyle name="Note 2" xfId="106"/>
-    <cellStyle name="Notiz 2" xfId="113"/>
-    <cellStyle name="Output 2" xfId="107"/>
-    <cellStyle name="Standaard_Business_List" xfId="108"/>
+    <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Accent1 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Accent2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Accent3 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Accent4 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Accent5 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Accent6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Bad 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Calculation 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Check Cell 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Good 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Heading 1 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Heading 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Heading 3 2" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Heading 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Input 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Linked Cell 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Neutral 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 10" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 10 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 10 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 10 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal 10 3" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Normal 10 4" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Normal 11" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Normal 11 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 11 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Normal 11 2 3" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Normal 11 3" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Normal 11 4" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 12" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Normal 12 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 12 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 12 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 13" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 13 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 13 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 13 4" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Normal 14" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Normal 14 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Normal 15" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Normal 15 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Normal 16" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Normal 17" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Normal 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Normal 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Normal 2 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Normal 2 5" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Normal 2 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Normal 3 2" xfId="76" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Normal 3 3" xfId="77" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Normal 3 4" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Normal 4" xfId="78" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Normal 4 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Normal 4 3" xfId="80" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Normal 5" xfId="81" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Normal 6" xfId="82" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Normal 6 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Normal 6 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Normal 7" xfId="85" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Normal 7 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Normal 7 2 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Normal 7 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Normal 7 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Normal 7 3 2" xfId="90" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Normal 7 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Normal 7 4" xfId="92" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Normal 7 5" xfId="93" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Normal 8" xfId="94" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Normal 8 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Normal 8 2 2" xfId="96" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Normal 8 2 3" xfId="97" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Normal 8 3" xfId="98" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Normal 8 4" xfId="99" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Normal 9" xfId="100" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Normal 9 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Normal 9 2 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Normal 9 2 3" xfId="103" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Normal 9 3" xfId="104" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Normal 9 4" xfId="105" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Note 2" xfId="106" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Notiz 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Output 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Standaard_Business_List" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="3"/>
-    <cellStyle name="Standard 3" xfId="112"/>
-    <cellStyle name="Title 2" xfId="109"/>
-    <cellStyle name="Total 2" xfId="110"/>
-    <cellStyle name="Warning Text 2" xfId="111"/>
+    <cellStyle name="Standard 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Standard 3" xfId="112" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Title 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Total 2" xfId="110" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Warning Text 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1748,14 +1760,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1793,9 +1808,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1828,9 +1843,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1863,9 +1895,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2038,50 +2087,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.265625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" style="16" customWidth="1"/>
     <col min="2" max="2" width="28" style="16" customWidth="1"/>
     <col min="3" max="4" width="12" style="16" customWidth="1"/>
-    <col min="5" max="5" width="22.59765625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="13.73046875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="16" customWidth="1"/>
     <col min="7" max="7" width="12" style="16" customWidth="1"/>
-    <col min="8" max="8" width="11.86328125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="4.3984375" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.59765625" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.265625" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.1328125" style="16" customWidth="1"/>
-    <col min="13" max="13" width="30.86328125" style="16" customWidth="1"/>
-    <col min="14" max="18" width="11.3984375" style="15"/>
-    <col min="19" max="16384" width="11.3984375" style="16"/>
+    <col min="8" max="8" width="11.85546875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="4.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" style="16" customWidth="1"/>
+    <col min="13" max="13" width="30.85546875" style="16" customWidth="1"/>
+    <col min="14" max="18" width="11.42578125" style="15"/>
+    <col min="19" max="16384" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="12" customFormat="1" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:18" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="69" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="70"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="69" t="s">
+      <c r="D1" s="50"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="69" t="s">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="70"/>
+      <c r="L1" s="50"/>
       <c r="M1" s="4" t="s">
         <v>28</v>
       </c>
@@ -2091,29 +2140,29 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="74" t="s">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
@@ -2134,7 +2183,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18"/>
       <c r="C4" s="19"/>
@@ -2149,7 +2198,7 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21"/>
       <c r="B5" s="22"/>
       <c r="C5" s="23"/>
@@ -2169,79 +2218,79 @@
       <c r="Q5" s="25"/>
       <c r="R5" s="25"/>
     </row>
-    <row r="6" spans="1:18" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="60" t="s">
+    <row r="6" spans="1:18" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
-    </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="63" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="42"/>
+    </row>
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
-    </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="66" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="45"/>
+    </row>
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="68"/>
-    </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="57" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="48"/>
+    </row>
+    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="47" t="s">
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="47" t="s">
+      <c r="F9" s="65"/>
+      <c r="G9" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="48"/>
-      <c r="I9" s="49" t="s">
+      <c r="H9" s="65"/>
+      <c r="I9" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="40" t="s">
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="57" t="s">
         <v>6</v>
       </c>
       <c r="N9" s="13"/>
@@ -2250,50 +2299,50 @@
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="43" t="s">
+    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="55"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="52" t="s">
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="41"/>
-    </row>
-    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="44"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
+      <c r="M10" s="58"/>
+    </row>
+    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="61"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
       <c r="I11" s="1" t="s">
         <v>0</v>
       </c>
@@ -2303,10 +2352,10 @@
       <c r="K11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="42"/>
-    </row>
-    <row r="12" spans="1:18" ht="12.75" x14ac:dyDescent="0.45">
+      <c r="L11" s="70"/>
+      <c r="M11" s="59"/>
+    </row>
+    <row r="12" spans="1:18" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A12" s="26"/>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
@@ -2321,7 +2370,7 @@
       <c r="L12" s="27"/>
       <c r="M12" s="29"/>
     </row>
-    <row r="13" spans="1:18" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
@@ -2336,7 +2385,7 @@
       <c r="L13" s="27"/>
       <c r="M13" s="29"/>
     </row>
-    <row r="14" spans="1:18" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A14" s="26"/>
       <c r="B14" s="27"/>
       <c r="C14" s="27"/>
@@ -2351,7 +2400,7 @@
       <c r="L14" s="27"/>
       <c r="M14" s="29"/>
     </row>
-    <row r="15" spans="1:18" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:18" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
@@ -2366,7 +2415,7 @@
       <c r="L15" s="27"/>
       <c r="M15" s="29"/>
     </row>
-    <row r="16" spans="1:18" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="27"/>
       <c r="C16" s="27"/>
@@ -2381,7 +2430,7 @@
       <c r="L16" s="27"/>
       <c r="M16" s="29"/>
     </row>
-    <row r="17" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -2396,7 +2445,7 @@
       <c r="L17" s="27"/>
       <c r="M17" s="29"/>
     </row>
-    <row r="18" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="27"/>
       <c r="C18" s="27"/>
@@ -2411,7 +2460,7 @@
       <c r="L18" s="27"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
@@ -2426,7 +2475,7 @@
       <c r="L19" s="27"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A20" s="26"/>
       <c r="B20" s="27"/>
       <c r="C20" s="27"/>
@@ -2441,7 +2490,7 @@
       <c r="L20" s="27"/>
       <c r="M20" s="29"/>
     </row>
-    <row r="21" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A21" s="26"/>
       <c r="B21" s="27"/>
       <c r="C21" s="27"/>
@@ -2456,7 +2505,7 @@
       <c r="L21" s="27"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A22" s="26"/>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
@@ -2471,7 +2520,7 @@
       <c r="L22" s="27"/>
       <c r="M22" s="29"/>
     </row>
-    <row r="23" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
       <c r="B23" s="27"/>
       <c r="C23" s="27"/>
@@ -2486,7 +2535,7 @@
       <c r="L23" s="27"/>
       <c r="M23" s="29"/>
     </row>
-    <row r="24" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -2501,7 +2550,7 @@
       <c r="L24" s="27"/>
       <c r="M24" s="29"/>
     </row>
-    <row r="25" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -2516,7 +2565,7 @@
       <c r="L25" s="27"/>
       <c r="M25" s="29"/>
     </row>
-    <row r="26" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A26" s="26"/>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -2531,7 +2580,7 @@
       <c r="L26" s="27"/>
       <c r="M26" s="29"/>
     </row>
-    <row r="27" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
@@ -2546,7 +2595,7 @@
       <c r="L27" s="27"/>
       <c r="M27" s="29"/>
     </row>
-    <row r="28" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -2561,7 +2610,7 @@
       <c r="L28" s="27"/>
       <c r="M28" s="29"/>
     </row>
-    <row r="29" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A29" s="26"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -2576,7 +2625,7 @@
       <c r="L29" s="27"/>
       <c r="M29" s="29"/>
     </row>
-    <row r="30" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A30" s="26"/>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -2591,7 +2640,7 @@
       <c r="L30" s="27"/>
       <c r="M30" s="29"/>
     </row>
-    <row r="31" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A31" s="26"/>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
@@ -2606,7 +2655,7 @@
       <c r="L31" s="27"/>
       <c r="M31" s="29"/>
     </row>
-    <row r="32" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -2621,7 +2670,7 @@
       <c r="L32" s="27"/>
       <c r="M32" s="29"/>
     </row>
-    <row r="33" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A33" s="26"/>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
@@ -2636,7 +2685,7 @@
       <c r="L33" s="27"/>
       <c r="M33" s="29"/>
     </row>
-    <row r="34" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A34" s="26"/>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -2651,7 +2700,7 @@
       <c r="L34" s="27"/>
       <c r="M34" s="29"/>
     </row>
-    <row r="35" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A35" s="26"/>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -2666,7 +2715,7 @@
       <c r="L35" s="27"/>
       <c r="M35" s="29"/>
     </row>
-    <row r="36" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A36" s="26"/>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
@@ -2681,7 +2730,7 @@
       <c r="L36" s="27"/>
       <c r="M36" s="29"/>
     </row>
-    <row r="37" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A37" s="26"/>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -2696,7 +2745,7 @@
       <c r="L37" s="27"/>
       <c r="M37" s="29"/>
     </row>
-    <row r="38" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A38" s="26"/>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
@@ -2711,7 +2760,7 @@
       <c r="L38" s="27"/>
       <c r="M38" s="29"/>
     </row>
-    <row r="39" spans="1:13" ht="12.75" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A39" s="31"/>
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
@@ -2726,7 +2775,7 @@
       <c r="L39" s="32"/>
       <c r="M39" s="34"/>
     </row>
-    <row r="40" spans="1:13" ht="13.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="35"/>
       <c r="B40" s="36"/>
       <c r="C40" s="36"/>
@@ -2741,17 +2790,9 @@
       <c r="L40" s="38"/>
       <c r="M40" s="39"/>
     </row>
-    <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:M2"/>
     <mergeCell ref="M9:M11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
@@ -2767,17 +2808,25 @@
     <mergeCell ref="L10:L11"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I5 I9:I1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I5 I9:I1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>31</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J5 J9:J1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J5 J9:J1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K5 K9:K1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K5 K9:K1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>1900</formula1>
       <formula2>2100</formula2>
     </dataValidation>
